--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rodrigo\Downloads\Projetos_Pessoais\Ações\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rodrigo\Downloads\Projetos_Pessoais\Ações\cruzamento_medias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BBADC91-8B5C-4607-9F56-F4E44546B8BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F7A49A-5AA9-4E5B-A0E7-3153FA9999B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,17 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>ticker</t>
   </si>
   <si>
-    <t>quantidade</t>
-  </si>
-  <si>
-    <t>preco_medio</t>
-  </si>
-  <si>
     <t>BIAU39</t>
   </si>
   <si>
@@ -61,33 +55,6 @@
   </si>
   <si>
     <t>TSLA34</t>
-  </si>
-  <si>
-    <t>116.57</t>
-  </si>
-  <si>
-    <t>122.52</t>
-  </si>
-  <si>
-    <t>139.34</t>
-  </si>
-  <si>
-    <t>13.87</t>
-  </si>
-  <si>
-    <t>115.22</t>
-  </si>
-  <si>
-    <t>11.22</t>
-  </si>
-  <si>
-    <t>10.92</t>
-  </si>
-  <si>
-    <t>307.74</t>
-  </si>
-  <si>
-    <t>37.82</t>
   </si>
 </sst>
 </file>
@@ -419,110 +386,52 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2">
-        <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>11</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6">
-        <v>50</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>300</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>1575</v>
-      </c>
-      <c r="C8" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>20</v>
-      </c>
-      <c r="C9" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10">
-        <v>120</v>
-      </c>
-      <c r="C10" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rodrigo\Downloads\Projetos_Pessoais\Ações\cruzamento_medias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3F7A49A-5AA9-4E5B-A0E7-3153FA9999B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC45AD77-AE42-4A2C-8473-4326B2920B14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,9 +45,6 @@
     <t>MSFT34</t>
   </si>
   <si>
-    <t>NFLX34</t>
-  </si>
-  <si>
     <t>NVDC34</t>
   </si>
   <si>
@@ -55,6 +52,9 @@
   </si>
   <si>
     <t>TSLA34</t>
+  </si>
+  <si>
+    <t>MUTC34</t>
   </si>
 </sst>
 </file>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rodrigo\Downloads\Projetos_Pessoais\Ações\cruzamento_medias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC45AD77-AE42-4A2C-8473-4326B2920B14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B199F64-A127-427D-BD23-1D115EB9354E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>ticker</t>
   </si>
@@ -55,6 +55,9 @@
   </si>
   <si>
     <t>MUTC34</t>
+  </si>
+  <si>
+    <t>AMZO34</t>
   </si>
 </sst>
 </file>
@@ -375,7 +378,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.42578125" customWidth="1"/>
@@ -434,6 +437,11 @@
         <v>9</v>
       </c>
     </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rodrigo\Downloads\Projetos_Pessoais\Ações\cruzamento_medias\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B199F64-A127-427D-BD23-1D115EB9354E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CD3A95F-A938-4E17-A7E9-1CF67E3968AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>ticker</t>
   </si>
@@ -58,6 +58,9 @@
   </si>
   <si>
     <t>AMZO34</t>
+  </si>
+  <si>
+    <t>W1DC34</t>
   </si>
 </sst>
 </file>
@@ -378,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.42578125" customWidth="1"/>
@@ -442,6 +445,11 @@
         <v>10</v>
       </c>
     </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rodrigo\Downloads\Projetos_Pessoais\Ações\cruzamento_medias\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rodrigo\Downloads\Projetos_Pessoais\Ações\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CD3A95F-A938-4E17-A7E9-1CF67E3968AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F5604E-A36D-42EE-9099-7CB4EDCC12E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3645" yWindow="825" windowWidth="22995" windowHeight="14280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>ticker</t>
   </si>
@@ -45,6 +45,9 @@
     <t>MSFT34</t>
   </si>
   <si>
+    <t>NFLX34</t>
+  </si>
+  <si>
     <t>NVDC34</t>
   </si>
   <si>
@@ -54,13 +57,7 @@
     <t>TSLA34</t>
   </si>
   <si>
-    <t>MUTC34</t>
-  </si>
-  <si>
-    <t>AMZO34</t>
-  </si>
-  <si>
-    <t>W1DC34</t>
+    <t>AURA33</t>
   </si>
 </sst>
 </file>
@@ -381,7 +378,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.42578125" customWidth="1"/>
@@ -445,11 +442,6 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rodrigo\Downloads\Projetos_Pessoais\Ações\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F5604E-A36D-42EE-9099-7CB4EDCC12E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FF32772-F41C-47D9-B6DA-93FEB0DB83E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3645" yWindow="825" windowWidth="22995" windowHeight="14280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>ticker</t>
   </si>
@@ -58,19 +58,28 @@
   </si>
   <si>
     <t>AURA33</t>
+  </si>
+  <si>
+    <t>MUTC34</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF474747"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -93,11 +102,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -378,7 +388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.42578125" customWidth="1"/>
@@ -442,6 +452,11 @@
         <v>10</v>
       </c>
     </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rodrigo\Downloads\Projetos_Pessoais\Ações\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FF32772-F41C-47D9-B6DA-93FEB0DB83E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A40BFE6E-52A5-43B8-A7C2-6437A820A49A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3645" yWindow="825" windowWidth="22995" windowHeight="14280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,14 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>ticker</t>
   </si>
   <si>
-    <t>BIAU39</t>
-  </si>
-  <si>
     <t>BSLV39</t>
   </si>
   <si>
@@ -45,9 +42,6 @@
     <t>MSFT34</t>
   </si>
   <si>
-    <t>NFLX34</t>
-  </si>
-  <si>
     <t>NVDC34</t>
   </si>
   <si>
@@ -57,10 +51,10 @@
     <t>TSLA34</t>
   </si>
   <si>
-    <t>AURA33</t>
-  </si>
-  <si>
     <t>MUTC34</t>
+  </si>
+  <si>
+    <t>AVGO34</t>
   </si>
 </sst>
 </file>
@@ -78,8 +72,9 @@
     <font>
       <sz val="11"/>
       <color rgb="FF474747"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -388,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.42578125" customWidth="1"/>
@@ -403,58 +398,48 @@
       <c r="C1" s="1"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
+      <c r="A2" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="A10" s="2" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rodrigo\Downloads\Projetos_Pessoais\Ações\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A40BFE6E-52A5-43B8-A7C2-6437A820A49A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2732985A-C883-4428-A97F-0D4BB88E289C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3645" yWindow="825" windowWidth="22995" windowHeight="14280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14055" yWindow="825" windowWidth="12585" windowHeight="14280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>ticker</t>
   </si>
@@ -39,9 +39,6 @@
     <t>M2ST34</t>
   </si>
   <si>
-    <t>MSFT34</t>
-  </si>
-  <si>
     <t>NVDC34</t>
   </si>
   <si>
@@ -55,6 +52,15 @@
   </si>
   <si>
     <t>AVGO34</t>
+  </si>
+  <si>
+    <t>ASML34</t>
+  </si>
+  <si>
+    <t>M2RV34</t>
+  </si>
+  <si>
+    <t>SPCX34</t>
   </si>
 </sst>
 </file>
@@ -97,12 +103,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -383,7 +392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.42578125" customWidth="1"/>
@@ -398,48 +407,60 @@
       <c r="C1" s="1"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
+      <c r="A3" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
